--- a/R_tips_for_advanced_use_byAsa/test.xlsx
+++ b/R_tips_for_advanced_use_byAsa/test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/asa/Documents/pre/R_tips_PengChen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC19AD8-B635-C745-A09D-41AC807FD1B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5117217E-6A7C-2447-B4E4-B838EB6648F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="580" yWindow="740" windowWidth="28240" windowHeight="17260" xr2:uid="{1F25317E-2107-C24A-8BDF-DEBEC5F067A0}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>mpg</t>
   </si>
@@ -83,6 +83,10 @@
   </si>
   <si>
     <t>Hornet Sportabout</t>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -450,6 +454,9 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:12">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
